--- a/05_Private_Credit/_template_CREDIT.xlsx
+++ b/05_Private_Credit/_template_CREDIT.xlsx
@@ -388,104 +388,108 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -744,54 +748,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -814,127 +818,127 @@
   <dimension ref="B2:C21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <f aca="false">C7+C8</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <f aca="false">C6*C19</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <f aca="false">C6</f>
         <v>0</v>
       </c>
@@ -958,119 +962,119 @@
   <dimension ref="B2:F12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="16" t="str">
+      <c r="D5" s="17" t="str">
         <f aca="false">IFERROR(Assumptions!C21/Assumptions!C14,"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="17" t="str">
+      <c r="E5" s="18" t="str">
         <f aca="false">IFERROR(C5-D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="D6" s="16" t="str">
+      <c r="D6" s="17" t="str">
         <f aca="false">IFERROR(Assumptions!C14/Assumptions!C20,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="18" t="str">
         <f aca="false">IFERROR(D6-C6,"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>1.2</v>
       </c>
-      <c r="D7" s="16" t="str">
+      <c r="D7" s="17" t="str">
         <f aca="false">IFERROR(Assumptions!C15/(Assumptions!C6*Assumptions!C9+Assumptions!C20),"-")</f>
         <v>-</v>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="18" t="str">
         <f aca="false">IFERROR(D7-C7,"-")</f>
         <v>-</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="str">
+      <c r="C10" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D5)),"-",IF(D5&lt;=C5,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="2" t="str">
+      <c r="C11" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D6)),"-",IF(D6&gt;=C6,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="2" t="str">
+      <c r="C12" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D7)),"-",IF(D7&gt;=C7,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
@@ -1094,200 +1098,200 @@
   <dimension ref="B2:H11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <f aca="false">Assumptions!C6</f>
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <f aca="false">C8</f>
         <v>0</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">D8</f>
         <v>0</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">E8</f>
         <v>0</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">F8</f>
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">G8</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
         <v>0</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
         <v>0</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
         <v>0</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
         <v>0</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
+      <c r="C7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <f aca="false">C5-C6-C7</f>
         <v>0</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <f aca="false">D5-D6-D7</f>
         <v>0</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <f aca="false">E5-E6-E7</f>
         <v>0</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="13" t="n">
         <f aca="false">F5-F6-F7</f>
         <v>0</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="13" t="n">
         <f aca="false">G5-G6-G7</f>
         <v>0</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="13" t="n">
         <f aca="false">H5-H6-H7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="13" t="n">
         <f aca="false">AVERAGE(C5,C8)*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <f aca="false">AVERAGE(D5,D8)*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <f aca="false">AVERAGE(E5,E8)*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="13" t="n">
         <f aca="false">AVERAGE(F5,F8)*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">AVERAGE(G5,G8)*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">AVERAGE(H5,H8)*Assumptions!$C$19</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="19" t="str">
+      <c r="C11" s="20" t="str">
         <f aca="false">IFERROR(C8/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="D11" s="19" t="str">
+      <c r="D11" s="20" t="str">
         <f aca="false">IFERROR(D8/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="E11" s="19" t="str">
+      <c r="E11" s="20" t="str">
         <f aca="false">IFERROR(E8/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="F11" s="19" t="str">
+      <c r="F11" s="20" t="str">
         <f aca="false">IFERROR(F8/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="G11" s="19" t="str">
+      <c r="G11" s="20" t="str">
         <f aca="false">IFERROR(G8/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="H11" s="19" t="str">
+      <c r="H11" s="20" t="str">
         <f aca="false">IFERROR(H8/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
@@ -1311,53 +1315,53 @@
   <dimension ref="B2:D8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <f aca="false">Assumptions!C19</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="22" t="n">
         <f aca="false">Assumptions!C9</f>
         <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">Assumptions!C10</f>
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <f aca="false">IFERROR((C4*100+(100-C5)/C6)/((100+C5)/2),"-")</f>
         <v>0.0969131371141421</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1380,104 +1384,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/05_Private_Credit/_template_CREDIT.xlsx
+++ b/05_Private_Credit/_template_CREDIT.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Covenants" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Debt Schedule" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Yield &amp; Spread" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Checks" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
   <si>
     <t xml:space="preserve">[BORROWER] — Private Credit / Debt Finance Model</t>
   </si>
@@ -105,6 +107,33 @@
     <t xml:space="preserve">Total debt ($, = drawn amount)</t>
   </si>
   <si>
+    <t xml:space="preserve">Excess Cash Flow (ECF) Sweep Step-Down Grid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard leveraged-loan credit-agreement provision: the sweep % of excess cash flow ratchets down as leverage falls, so a borrower keeps more cash once it's delevered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leverage &gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep % of ECF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Below Tier 3 threshold</t>
+  </si>
+  <si>
     <t xml:space="preserve">Covenant Headroom</t>
   </si>
   <si>
@@ -156,6 +185,9 @@
     <t xml:space="preserve">Debt Schedule</t>
   </si>
   <si>
+    <t xml:space="preserve">Interest and the ECF sweep tier both key off the BEGINNING-of-period balance — never the period's own ending balance — so nothing here is circular.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yr0</t>
   </si>
   <si>
@@ -180,15 +212,21 @@
     <t xml:space="preserve">Mandatory amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash sweep (excess CFADS, if any)</t>
+    <t xml:space="preserve">Beginning-of-period leverage (for ECF tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECF sweep % (step-down grid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest expense (all-in rate x beginning balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash sweep (Excess Cash Flow: CFADS less scheduled debt service, x tier %)</t>
   </si>
   <si>
     <t xml:space="preserve">Ending balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Interest expense (all-in rate x avg balance)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leverage (ending debt / EBITDA)</t>
   </si>
   <si>
@@ -205,6 +243,93 @@
   </si>
   <si>
     <t xml:space="preserve">Standard bond-math approximation: (Coupon$+(100-Price)/n)/((100+Price)/2). At par (Price=100) this collapses to the coupon rate exactly — sanity check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECF sweep step-down grid (75%/50%/25%/0% by leverage tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard leveraged-loan credit-agreement provision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative tier thresholds/percentages — not any specific credit agreement's actual terms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covenant thresholds (5.0x leverage, 2.5x interest coverage, 1.2x DSCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[fill in — actual credit agreement]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder defaults; replace with the specific facility's real covenant levels before use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approximate YTM: (coupon$+(100-price)/n)/((100+price)/2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard bond-math approximation for yield including OID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approximation, not an exact IRR solve — collapses to the coupon rate exactly at par (Price=100), the built-in sanity check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest computed off beginning-of-period balance only (not average)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling convention used throughout this repo to avoid circular references between interest and the ECF sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slightly understates true average-balance interest expense when the balance amortizes or sweeps within the period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ending balance ties: beginning - amort - sweep = ending (Yr5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roll-forward ties: next period's beginning = this period's ending (Yr0-&gt;Yr1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total debt (Assumptions) ties to Debt Schedule Yr0 beginning balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECF sweep never negative (MAX floor holds across the full schedule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -229,7 +354,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00%;\(0.00%\);\-"/>
@@ -237,6 +362,7 @@
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="170" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -297,17 +423,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -388,108 +514,124 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -748,54 +890,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -815,131 +957,192 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C21"/>
+  <dimension ref="B2:D28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="11" t="n">
         <f aca="false">C7+C8</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="12" t="n">
         <f aca="false">C6*C19</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="13" t="n">
         <f aca="false">C6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -962,119 +1165,119 @@
   <dimension ref="B2:F12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>26</v>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>32</v>
+      <c r="B5" s="0" t="s">
+        <v>41</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="17" t="str">
+      <c r="D5" s="18" t="str">
         <f aca="false">IFERROR(Assumptions!C21/Assumptions!C14,"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="18" t="str">
+      <c r="E5" s="19" t="str">
         <f aca="false">IFERROR(C5-D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>33</v>
+      <c r="F5" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>34</v>
+      <c r="B6" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="D6" s="17" t="str">
+      <c r="D6" s="18" t="str">
         <f aca="false">IFERROR(Assumptions!C14/Assumptions!C20,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="18" t="str">
+      <c r="E6" s="19" t="str">
         <f aca="false">IFERROR(D6-C6,"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>35</v>
+      <c r="F6" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>36</v>
+      <c r="B7" s="0" t="s">
+        <v>45</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>1.2</v>
       </c>
-      <c r="D7" s="17" t="str">
-        <f aca="false">IFERROR(Assumptions!C15/(Assumptions!C6*Assumptions!C9+Assumptions!C20),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E7" s="18" t="str">
+      <c r="D7" s="18" t="str">
+        <f aca="false">IFERROR(Assumptions!C15/(Assumptions!C6*Assumptions!C11+Assumptions!C20),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E7" s="19" t="str">
         <f aca="false">IFERROR(D7-C7,"-")</f>
         <v>-</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>37</v>
+      <c r="F7" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>38</v>
+      <c r="B9" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="3" t="str">
+      <c r="B10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D5)),"-",IF(D5&lt;=C5,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="str">
+      <c r="B11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D6)),"-",IF(D6&gt;=C6,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="3" t="str">
+      <c r="B12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="2" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D7)),"-",IF(D7&gt;=C7,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
@@ -1095,204 +1298,273 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:H11"/>
+  <dimension ref="B2:H14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>48</v>
+      <c r="B2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <f aca="false">Assumptions!C6</f>
         <v>0</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <f aca="false">C8</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <f aca="false">D8</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <f aca="false">E8</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <f aca="false">F8</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <f aca="false">G8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <f aca="false">Assumptions!$C$6*Assumptions!$C$9</f>
+      <c r="D6" s="12" t="n">
+        <f aca="false">C12</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <f aca="false">D12</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <f aca="false">E12</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <f aca="false">F12</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <f aca="false">G12</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13" t="n">
+      <c r="B7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <f aca="false">C5-C6-C7</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <f aca="false">D5-D6-D7</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <f aca="false">E5-E6-E7</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <f aca="false">F5-F6-F7</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <f aca="false">G5-G6-G7</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <f aca="false">H5-H6-H7</f>
-        <v>0</v>
+      <c r="B8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="19" t="str">
+        <f aca="false">IFERROR(C6/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="19" t="str">
+        <f aca="false">IFERROR(D6/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E8" s="19" t="str">
+        <f aca="false">IFERROR(E6/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="19" t="str">
+        <f aca="false">IFERROR(F6/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="19" t="str">
+        <f aca="false">IFERROR(G6/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H8" s="19" t="str">
+        <f aca="false">IFERROR(H6/Assumptions!$C$14,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <f aca="false">AVERAGE(C5,C8)*Assumptions!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <f aca="false">AVERAGE(D5,D8)*Assumptions!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <f aca="false">AVERAGE(E5,E8)*Assumptions!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <f aca="false">AVERAGE(F5,F8)*Assumptions!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <f aca="false">AVERAGE(G5,G8)*Assumptions!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <f aca="false">AVERAGE(H5,H8)*Assumptions!$C$19</f>
+      <c r="B9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <f aca="false">IF(NOT(ISNUMBER(C8)),0,IF(C8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(C8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(C8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <f aca="false">IF(NOT(ISNUMBER(D8)),0,IF(D8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(D8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(D8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <f aca="false">IF(NOT(ISNUMBER(E8)),0,IF(E8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(E8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(E8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <f aca="false">IF(NOT(ISNUMBER(F8)),0,IF(F8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(F8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(F8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <f aca="false">IF(NOT(ISNUMBER(G8)),0,IF(G8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(G8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(G8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <f aca="false">IF(NOT(ISNUMBER(H8)),0,IF(H8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(H8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(H8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <f aca="false">C6*Assumptions!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <f aca="false">D6*Assumptions!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">E6*Assumptions!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <f aca="false">F6*Assumptions!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <f aca="false">G6*Assumptions!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <f aca="false">H6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="20" t="str">
-        <f aca="false">IFERROR(C8/Assumptions!$C$14,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D11" s="20" t="str">
-        <f aca="false">IFERROR(D8/Assumptions!$C$14,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E11" s="20" t="str">
-        <f aca="false">IFERROR(E8/Assumptions!$C$14,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F11" s="20" t="str">
-        <f aca="false">IFERROR(F8/Assumptions!$C$14,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G11" s="20" t="str">
-        <f aca="false">IFERROR(G8/Assumptions!$C$14,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H11" s="20" t="str">
-        <f aca="false">IFERROR(H8/Assumptions!$C$14,"-")</f>
+      <c r="B11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <f aca="false">MAX(Assumptions!$C$15-C10-C7,0)*C9</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <f aca="false">MAX(Assumptions!$C$15-D10-D7,0)*D9</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <f aca="false">MAX(Assumptions!$C$15-E10-E7,0)*E9</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <f aca="false">MAX(Assumptions!$C$15-F10-F7,0)*F9</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <f aca="false">MAX(Assumptions!$C$15-G10-G7,0)*G9</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <f aca="false">MAX(Assumptions!$C$15-H10-H7,0)*H9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <f aca="false">C6-C7-C11</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <f aca="false">D6-D7-D11</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <f aca="false">E6-E7-E11</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <f aca="false">F6-F7-F11</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <f aca="false">G6-G7-G11</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <f aca="false">H6-H7-H11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="21" t="str">
+        <f aca="false">IFERROR(C12/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D14" s="21" t="str">
+        <f aca="false">IFERROR(D12/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E14" s="21" t="str">
+        <f aca="false">IFERROR(E12/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F14" s="21" t="str">
+        <f aca="false">IFERROR(F12/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G14" s="21" t="str">
+        <f aca="false">IFERROR(G12/Assumptions!$C$14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H14" s="21" t="str">
+        <f aca="false">IFERROR(H12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -1315,54 +1587,54 @@
   <dimension ref="B2:D8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>55</v>
+      <c r="B2" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="21" t="n">
+      <c r="B4" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="22" t="n">
         <f aca="false">Assumptions!C19</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="22" t="n">
+      <c r="B5" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="23" t="n">
         <f aca="false">Assumptions!C9</f>
         <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">Assumptions!C10</f>
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="24" t="n">
+      <c r="B8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="25" t="n">
         <f aca="false">IFERROR((C4*100+(100-C5)/C6)/((100+C5)/2),"-")</f>
         <v>0.0969131371141421</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>59</v>
+      <c r="D8" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1381,107 +1653,307 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <f aca="false">'Debt Schedule'!H12-('Debt Schedule'!H6-'Debt Schedule'!H7-'Debt Schedule'!H11)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <f aca="false">'Debt Schedule'!D6-'Debt Schedule'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <f aca="false">Assumptions!C21-'Debt Schedule'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="29" t="b">
+        <f aca="false">IF(MIN('Debt Schedule'!C11:H11)&gt;=0,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>60</v>
+      <c r="B2" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/05_Private_Credit/_template_CREDIT.xlsx
+++ b/05_Private_Credit/_template_CREDIT.xlsx
@@ -519,119 +519,119 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -890,54 +890,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -960,189 +960,189 @@
   <dimension ref="B2:D28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <f aca="false">C7+C8</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <f aca="false">C6*C19</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <f aca="false">C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="11" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="11" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="10" t="n">
+      <c r="C28" s="18"/>
+      <c r="D28" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1165,119 +1165,119 @@
   <dimension ref="B2:F12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="18" t="str">
+      <c r="D5" s="19" t="str">
         <f aca="false">IFERROR(Assumptions!C21/Assumptions!C14,"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="19" t="str">
+      <c r="E5" s="20" t="str">
         <f aca="false">IFERROR(C5-D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="D6" s="18" t="str">
+      <c r="D6" s="19" t="str">
         <f aca="false">IFERROR(Assumptions!C14/Assumptions!C20,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="19" t="str">
+      <c r="E6" s="20" t="str">
         <f aca="false">IFERROR(D6-C6,"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="D7" s="18" t="str">
+      <c r="D7" s="19" t="str">
         <f aca="false">IFERROR(Assumptions!C15/(Assumptions!C6*Assumptions!C11+Assumptions!C20),"-")</f>
         <v>-</v>
       </c>
-      <c r="E7" s="19" t="str">
+      <c r="E7" s="20" t="str">
         <f aca="false">IFERROR(D7-C7,"-")</f>
         <v>-</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="2" t="str">
+      <c r="C10" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D5)),"-",IF(D5&lt;=C5,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="2" t="str">
+      <c r="C11" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D6)),"-",IF(D6&gt;=C6,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="2" t="str">
+      <c r="C12" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(D7)),"-",IF(D7&gt;=C7,"PASS","BREACH"))</f>
         <v>-</v>
       </c>
@@ -1301,269 +1301,269 @@
   <dimension ref="B2:H14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">Assumptions!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">C12</f>
         <v>0</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">D12</f>
         <v>0</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">E12</f>
         <v>0</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">F12</f>
         <v>0</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">G12</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$11</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="19" t="str">
+      <c r="C8" s="20" t="str">
         <f aca="false">IFERROR(C6/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="D8" s="19" t="str">
+      <c r="D8" s="20" t="str">
         <f aca="false">IFERROR(D6/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="19" t="str">
+      <c r="E8" s="20" t="str">
         <f aca="false">IFERROR(E6/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="F8" s="19" t="str">
+      <c r="F8" s="20" t="str">
         <f aca="false">IFERROR(F6/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="G8" s="19" t="str">
+      <c r="G8" s="20" t="str">
         <f aca="false">IFERROR(G6/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="H8" s="19" t="str">
+      <c r="H8" s="20" t="str">
         <f aca="false">IFERROR(H6/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <f aca="false">IF(NOT(ISNUMBER(C8)),0,IF(C8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(C8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(C8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
         <v>0</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">IF(NOT(ISNUMBER(D8)),0,IF(D8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(D8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(D8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">IF(NOT(ISNUMBER(E8)),0,IF(E8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(E8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(E8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <f aca="false">IF(NOT(ISNUMBER(F8)),0,IF(F8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(F8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(F8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <f aca="false">IF(NOT(ISNUMBER(G8)),0,IF(G8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(G8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(G8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <f aca="false">IF(NOT(ISNUMBER(H8)),0,IF(H8&gt;Assumptions!$C$25,Assumptions!$D$25,IF(H8&gt;Assumptions!$C$26,Assumptions!$D$26,IF(H8&gt;Assumptions!$C$27,Assumptions!$D$27,Assumptions!$D$28))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <f aca="false">C6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <f aca="false">D6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <f aca="false">E6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="13" t="n">
         <f aca="false">F6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="13" t="n">
         <f aca="false">G6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">H6*Assumptions!$C$19</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <f aca="false">MAX(Assumptions!$C$15-C10-C7,0)*C9</f>
         <v>0</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <f aca="false">MAX(Assumptions!$C$15-D10-D7,0)*D9</f>
         <v>0</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <f aca="false">MAX(Assumptions!$C$15-E10-E7,0)*E9</f>
         <v>0</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <f aca="false">MAX(Assumptions!$C$15-F10-F7,0)*F9</f>
         <v>0</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <f aca="false">MAX(Assumptions!$C$15-G10-G7,0)*G9</f>
         <v>0</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">MAX(Assumptions!$C$15-H10-H7,0)*H9</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="13" t="n">
         <f aca="false">C6-C7-C11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <f aca="false">D6-D7-D11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <f aca="false">E6-E7-E11</f>
         <v>0</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <f aca="false">F6-F7-F11</f>
         <v>0</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="13" t="n">
         <f aca="false">G6-G7-G11</f>
         <v>0</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="13" t="n">
         <f aca="false">H6-H7-H11</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="21" t="str">
+      <c r="C14" s="22" t="str">
         <f aca="false">IFERROR(C12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="D14" s="21" t="str">
+      <c r="D14" s="22" t="str">
         <f aca="false">IFERROR(D12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="E14" s="21" t="str">
+      <c r="E14" s="22" t="str">
         <f aca="false">IFERROR(E12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="F14" s="21" t="str">
+      <c r="F14" s="22" t="str">
         <f aca="false">IFERROR(F12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="G14" s="21" t="str">
+      <c r="G14" s="22" t="str">
         <f aca="false">IFERROR(G12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
-      <c r="H14" s="21" t="str">
+      <c r="H14" s="22" t="str">
         <f aca="false">IFERROR(H12/Assumptions!$C$14,"-")</f>
         <v>-</v>
       </c>
@@ -1587,53 +1587,53 @@
   <dimension ref="B2:D8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="23" t="n">
         <f aca="false">Assumptions!C19</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="24" t="n">
         <f aca="false">Assumptions!C9</f>
         <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">Assumptions!C10</f>
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">IFERROR((C4*100+(100-C5)/C6)/((100+C5)/2),"-")</f>
         <v>0.0969131371141421</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1656,90 +1656,90 @@
   <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="28" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="28" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="28" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="28" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1762,78 +1762,78 @@
   <dimension ref="B2:D9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <f aca="false">'Debt Schedule'!H12-('Debt Schedule'!H6-'Debt Schedule'!H7-'Debt Schedule'!H11)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <f aca="false">'Debt Schedule'!D6-'Debt Schedule'!C12</f>
         <v>0</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <f aca="false">Assumptions!C21-'Debt Schedule'!C6</f>
         <v>0</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="27" t="s">
         <v>99</v>
       </c>
       <c r="C9" s="29" t="b">
         <f aca="false">IF(MIN('Debt Schedule'!C11:H11)&gt;=0,TRUE(),FALSE())</f>
         <v>1</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1856,104 +1856,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
